--- a/output/full_scan/batch_seq4_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq4_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:O160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>3231</v>
+        <v>3529</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>737.9987830226459</v>
+        <v>773.2069553507322</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>193</v>
+        <v>2835</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.23752339286851</v>
+        <v>57.85060198881289</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.80548734614509</v>
+        <v>19.98084982293318</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.6913153777395875</v>
+        <v>1.627423699629444</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.425083512124845</v>
+        <v>80.02114169646455</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>3416</v>
+        <v>3231</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>融程電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>729.2544067962781</v>
+        <v>737.9987830226459</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.98158937135435</v>
+        <v>64.23752339286851</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.72195137408307</v>
+        <v>24.80548734614509</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.525440679627806</v>
+        <v>0.6913153777395875</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.689223396144932</v>
+        <v>2.425083512124845</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>3652</v>
+        <v>3416</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>精聯</t>
+          <t>融程電</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>728.6058075439404</v>
+        <v>729.2544067962781</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>36.65</v>
+        <v>196</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.39804736011274</v>
+        <v>63.98158937135435</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>22.22741131272977</v>
+        <v>16.72195137408307</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.685735948062797</v>
+        <v>1.525440679627806</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7545434388165833</v>
+        <v>2.689223396144932</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3490</v>
+        <v>3652</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>單井</t>
+          <t>精聯</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>724.7106404914687</v>
+        <v>728.6058075439404</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.6</v>
+        <v>36.65</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.18804716583239</v>
+        <v>62.39804736011274</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.51108561332508</v>
+        <v>22.22741131272977</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.571064049146862</v>
+        <v>4.685735948062797</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.6417741542745894</v>
+        <v>0.7545434388165833</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3704</v>
+        <v>3490</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>單井</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>711.5924439320138</v>
+        <v>724.7106404914687</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>50.4</v>
+        <v>31.6</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.53308292979008</v>
+        <v>60.18804716583239</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>13.97917781226429</v>
+        <v>24.51108561332508</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.614905865343557</v>
+        <v>3.571064049146862</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,48 +835,48 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4819674184497522</v>
+        <v>0.6417741542745894</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3454</v>
+        <v>3704</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>晶睿</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>685.7898084125552</v>
+        <v>711.5924439320138</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>99.40000000000001</v>
+        <v>50.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.51901815126084</v>
+        <v>59.53308292979008</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>60.67005946208872</v>
+        <v>13.97917781226429</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.9653194621989536</v>
+        <v>2.614905865343557</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,84 +888,84 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.0528038278700647</v>
+        <v>0.4819674184497522</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3211</v>
+        <v>3454</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>晶睿</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>675.3247075254499</v>
+        <v>685.7898084125552</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>370</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>51.12202035336713</v>
+        <v>63.51901815126084</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>19.96916632634421</v>
+        <v>60.67005946208872</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.998092092298722</v>
+        <v>0.9653194621989536</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.829495552506135</v>
+        <v>-0.0528038278700647</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3363</v>
+        <v>3211</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>664.7397012885942</v>
+        <v>675.3247075254499</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>640</v>
+        <v>370</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.96395157601239</v>
+        <v>51.12202035336713</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.08044866225858</v>
+        <v>19.96916632634421</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8850533929591936</v>
+        <v>1.998092092298722</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>17.38175889512833</v>
+        <v>2.829495552506135</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3234</v>
+        <v>3363</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>光環</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>636.6118109716069</v>
+        <v>664.7397012885942</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>118</v>
+        <v>640</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.48694885220877</v>
+        <v>56.96395157601239</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.46200899238038</v>
+        <v>21.08044866225858</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.600401862650045</v>
+        <v>0.8850533929591936</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.202309914564224</v>
+        <v>17.38175889512833</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3229</v>
+        <v>3234</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>晟鈦</t>
+          <t>光環</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>633.9096059227943</v>
+        <v>636.6118109716069</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>50.9</v>
+        <v>118</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.67920624425091</v>
+        <v>55.48694885220877</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18.77732465110371</v>
+        <v>14.46200899238038</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.990960592279432</v>
+        <v>1.600401862650045</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.054148393769674</v>
+        <v>2.202309914564224</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3605</v>
+        <v>3229</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>宏致</t>
+          <t>晟鈦</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>629.9031701812129</v>
+        <v>633.9096059227943</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>109</v>
+        <v>50.9</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>69.70183232920758</v>
+        <v>64.67920624425091</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.70343151008334</v>
+        <v>18.77732465110371</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.090317018121284</v>
+        <v>1.990960592279432</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.455179238543279</v>
+        <v>1.054148393769674</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3287</v>
+        <v>3605</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>廣寰科</t>
+          <t>宏致</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>626.1833632249621</v>
+        <v>629.9031701812129</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>31.15</v>
+        <v>109</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.75691532546559</v>
+        <v>69.70183232920758</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23.72558595799079</v>
+        <v>20.70343151008334</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.157696214557733</v>
+        <v>1.090317018121284</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3902196928272468</v>
+        <v>2.455179238543279</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3310</v>
+        <v>3287</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>佳穎</t>
+          <t>廣寰科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>599.0781350575568</v>
+        <v>626.1833632249621</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>31.15</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>64.38174484277395</v>
+        <v>57.75691532546559</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18.34777082770783</v>
+        <v>23.72558595799079</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.91447419575297</v>
+        <v>2.157696214557733</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2856343571997617</v>
+        <v>0.3902196928272468</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3264</v>
+        <v>3310</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>佳穎</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>593.6729164739097</v>
+        <v>599.0781350575568</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>222.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.71596433463883</v>
+        <v>64.38174484277395</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14.87028360233367</v>
+        <v>18.34777082770783</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2.228701683596052</v>
+        <v>0.91447419575297</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.368831982714045</v>
+        <v>0.2856343571997617</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3135</v>
+        <v>3264</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>591.8226943259202</v>
+        <v>593.6729164739097</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>163</v>
+        <v>222.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>48.73196640918998</v>
+        <v>55.71596433463883</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27.31729523965171</v>
+        <v>14.87028360233367</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.56043382196469</v>
+        <v>2.228701683596052</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>3.76481088422747</v>
+        <v>3.368831982714045</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3213</v>
+        <v>3135</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>茂訊</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>584.6426803619668</v>
+        <v>591.8226943259202</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.91608900351107</v>
+        <v>48.73196640918998</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.26251512492098</v>
+        <v>27.31729523965171</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.080528422749726</v>
+        <v>1.56043382196469</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.579847949389937</v>
+        <v>3.76481088422747</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3706</v>
+        <v>3213</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>茂訊</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>572.4675514492659</v>
+        <v>584.6426803619668</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>138</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.97115774040297</v>
+        <v>60.91608900351107</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8.731103516336859</v>
+        <v>17.26251512492098</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6368154823161221</v>
+        <v>1.080528422749726</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3592028875458998</v>
+        <v>1.579847949389937</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3543</v>
+        <v>3706</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>州巧</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>567.8214413269366</v>
+        <v>572.4675514492659</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.75</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>70.1534588095339</v>
+        <v>57.97115774040297</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.0827059065673</v>
+        <v>8.731103516336859</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.401340683166872</v>
+        <v>0.6368154823161221</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.060752250050814</v>
+        <v>0.3592028875458998</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3131</v>
+        <v>3543</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>州巧</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>562.4543449079785</v>
+        <v>567.8214413269366</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2470</v>
+        <v>37.75</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.95965385234437</v>
+        <v>70.1534588095339</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>24.20420292593326</v>
+        <v>28.0827059065673</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.340726747450045</v>
+        <v>1.401340683166872</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-9.615153468237366</v>
+        <v>1.060752250050814</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3617</v>
+        <v>3131</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>556.0309281117148</v>
+        <v>562.4543449079785</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>234</v>
+        <v>2470</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.82716681411814</v>
+        <v>40.95965385234437</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17.8448411216491</v>
+        <v>24.20420292593326</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6652409795986982</v>
+        <v>1.340726747450045</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.45939348049718</v>
+        <v>-9.615153468237366</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3434</v>
+        <v>3617</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>哲固</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>545.8436794823249</v>
+        <v>556.0309281117148</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>31.55</v>
+        <v>234</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.2710146927483</v>
+        <v>61.82716681411814</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9.412432920036675</v>
+        <v>17.8448411216491</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.313388205049885</v>
+        <v>0.6652409795986982</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2193141231204714</v>
+        <v>2.45939348049718</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3450</v>
+        <v>3434</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>哲固</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>540.9838202852139</v>
+        <v>545.8436794823249</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>524</v>
+        <v>31.55</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>59.12248340615828</v>
+        <v>63.2710146927483</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>17.18159744672563</v>
+        <v>9.412432920036675</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.292444621629917</v>
+        <v>1.313388205049885</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>13.57708698704883</v>
+        <v>0.2193141231204714</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3702</v>
+        <v>3450</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>540.2761845396217</v>
+        <v>540.9838202852139</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>130</v>
+        <v>524</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.2548279259393</v>
+        <v>59.12248340615828</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.04986264186702</v>
+        <v>17.18159744672563</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.9215575166350304</v>
+        <v>1.292444621629917</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.630033604118469</v>
+        <v>13.57708698704883</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3339</v>
+        <v>3702</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>533.3318856470146</v>
+        <v>540.2761845396217</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>39.5</v>
+        <v>130</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.701020981751</v>
+        <v>63.2548279259393</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.50391042350564</v>
+        <v>19.04986264186702</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.833188564701453</v>
+        <v>0.9215575166350304</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.038199870772954</v>
+        <v>1.630033604118469</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3441</v>
+        <v>3339</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聯一光</t>
+          <t>泰谷</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>528.5122934095341</v>
+        <v>533.3318856470146</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>79.5</v>
+        <v>39.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.92204308725844</v>
+        <v>53.701020981751</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.17915349396331</v>
+        <v>21.50391042350564</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4905539434476214</v>
+        <v>1.833188564701453</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.7115976637858545</v>
+        <v>1.038199870772954</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3515</v>
+        <v>3441</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>聯一光</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>521.7465230627205</v>
+        <v>528.5122934095341</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>215.5</v>
+        <v>79.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.17638119636297</v>
+        <v>51.92204308725844</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.8355530653896</v>
+        <v>31.17915349396331</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.229332146471959</v>
+        <v>0.4905539434476214</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>3.065341551260901</v>
+        <v>0.7115976637858545</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3576</v>
+        <v>3515</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聯合再生</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>521.1336037725871</v>
+        <v>521.7465230627205</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17.15</v>
+        <v>215.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>48.84812940525865</v>
+        <v>55.17638119636297</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>10.95116596838298</v>
+        <v>25.8355530653896</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3975140045186208</v>
+        <v>1.229332146471959</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0005798858309678</v>
+        <v>3.065341551260901</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3236</v>
+        <v>3576</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>千如</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>515.2551049095487</v>
+        <v>521.1336037725871</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>42.95</v>
+        <v>17.15</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>42.762172385728</v>
+        <v>48.84812940525865</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.82966662494544</v>
+        <v>10.95116596838298</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5061119685887816</v>
+        <v>0.3975140045186208</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.4445312600089295</v>
+        <v>0.0005798858309678</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3305</v>
+        <v>3236</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>昇貿</t>
+          <t>千如</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>511.3759141296471</v>
+        <v>515.2551049095487</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>115</v>
+        <v>42.95</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.35754371788809</v>
+        <v>42.762172385728</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30.01432610678187</v>
+        <v>27.82966662494544</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.844527760562626</v>
+        <v>0.5061119685887816</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>2.332636757373004</v>
+        <v>0.4445312600089295</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3432</v>
+        <v>3305</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>台端</t>
+          <t>昇貿</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>509.1276656176567</v>
+        <v>511.3759141296471</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>16.3</v>
+        <v>115</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>44.46841729648209</v>
+        <v>50.35754371788809</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26.17095465594711</v>
+        <v>30.01432610678187</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.428564160916538</v>
+        <v>1.844527760562626</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0313564851147131</v>
+        <v>2.332636757373004</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3228</v>
+        <v>3432</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>金麗科</t>
+          <t>台端</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>503.6554356451087</v>
+        <v>509.1276656176567</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>144.5</v>
+        <v>16.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40.62603471694357</v>
+        <v>44.46841729648209</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.81622321564722</v>
+        <v>26.17095465594711</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9582166095686722</v>
+        <v>1.428564160916538</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.5134639006643855</v>
+        <v>0.0313564851147131</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3406</v>
+        <v>3228</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>金麗科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>496.6431072444411</v>
+        <v>503.6554356451087</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>546</v>
+        <v>144.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.78407420290111</v>
+        <v>40.62603471694357</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.42385370188866</v>
+        <v>30.81622321564722</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.695183629520082</v>
+        <v>0.9582166095686722</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>10.50884951910183</v>
+        <v>0.5134639006643855</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3550</v>
+        <v>3520</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>聯穎</t>
+          <t>華盈</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>483.5336539912813</v>
+        <v>500.2714505324216</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>23.7</v>
+        <v>18.55</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>49.64805253251437</v>
+        <v>61.54269212122929</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23.7622876670097</v>
+        <v>18.19142370795009</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.312902454111156</v>
+        <v>0.5161800606409446</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.5146955299573275</v>
+        <v>0.1244895401641533</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3504</v>
+        <v>3406</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>478.7404876997522</v>
+        <v>496.6431072444411</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>546</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.17356910356891</v>
+        <v>49.78407420290111</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.45024209050174</v>
+        <v>23.42385370188866</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2780986967643438</v>
+        <v>1.695183629520082</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.4531452950276</v>
+        <v>10.50884951910183</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3711</v>
+        <v>3499</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>環天科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>477.7928207972921</v>
+        <v>488.3264077541515</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>630</v>
+        <v>13.05</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.67713880353942</v>
+        <v>38.10908518247746</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.24725510608981</v>
+        <v>33.5176236632549</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.218335716211246</v>
+        <v>0.3463732437251297</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>2.444940034808628</v>
+        <v>0.009328583959975901</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3388</v>
+        <v>3550</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>崇越電</t>
+          <t>聯穎</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>472.9362358848501</v>
+        <v>483.5336539912813</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>41.31890522641645</v>
+        <v>49.64805253251437</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.19186167618952</v>
+        <v>23.7622876670097</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8321548011603138</v>
+        <v>2.312902454111156</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.810028106860869</v>
+        <v>0.5146955299573275</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3714</v>
+        <v>3504</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>469.9959781473718</v>
+        <v>478.7404876997522</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>59</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.29842960687191</v>
+        <v>52.17356910356891</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.08323476358289</v>
+        <v>23.45024209050174</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.359763832005223</v>
+        <v>0.2780986967643438</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.481487393918177</v>
+        <v>1.4531452950276</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3518</v>
+        <v>3711</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>柏騰</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>468.4205817212333</v>
+        <v>477.7928207972921</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>28.25</v>
+        <v>630</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>53.91720275829047</v>
+        <v>53.67713880353942</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.04224499127738</v>
+        <v>17.24725510608981</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.731242847907468</v>
+        <v>1.218335716211246</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.4107032253139413</v>
+        <v>2.444940034808628</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3402</v>
+        <v>3388</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>崇越電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>468.403283649527</v>
+        <v>472.9362358848501</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>129.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.09093946567858</v>
+        <v>41.31890522641645</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.08414713541877</v>
+        <v>29.19186167618952</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2823479372927758</v>
+        <v>0.8321548011603138</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0217720869491113</v>
+        <v>0.810028106860869</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>3583</v>
+        <v>3714</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>457.7619267822797</v>
+        <v>469.9959781473718</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>696</v>
+        <v>59</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>44.89816132688742</v>
+        <v>55.29842960687191</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20.79789618121525</v>
+        <v>16.08323476358289</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6016276262522575</v>
+        <v>2.359763832005223</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>4.431115853590128</v>
+        <v>1.481487393918177</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>3224</v>
+        <v>3518</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>三顧</t>
+          <t>柏騰</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>455.5613901365115</v>
+        <v>468.4205817212333</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>36.8</v>
+        <v>28.25</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>55.37684587293788</v>
+        <v>53.91720275829047</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>24.63797840350205</v>
+        <v>23.04224499127738</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.064490791459104</v>
+        <v>2.731242847907468</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2814236382594555</v>
+        <v>0.4107032253139413</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>3592</v>
+        <v>3402</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>445.3907212797503</v>
+        <v>468.403283649527</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>244</v>
+        <v>129.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.11204283484098</v>
+        <v>46.09093946567858</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>33.13173123647515</v>
+        <v>20.08414713541877</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8877225358544597</v>
+        <v>0.2823479372927758</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>2.574958113918338</v>
+        <v>0.0217720869491113</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>3479</v>
+        <v>3498</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>安勤</t>
+          <t>陽程</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>442.3533246452407</v>
+        <v>467.8234925553313</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.49090487187561</v>
+        <v>59.00630840070318</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.94432343552602</v>
+        <v>17.28565101125536</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4023027898990143</v>
+        <v>1.121779873079941</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.4909421766267287</v>
+        <v>2.614502756752201</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3661</v>
+        <v>3583</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>441.9220853793421</v>
+        <v>457.7619267822797</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>3800</v>
+        <v>696</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.45548560347702</v>
+        <v>44.89816132688742</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17.36339353751946</v>
+        <v>20.79789618121525</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.492208537934204</v>
+        <v>0.6016276262522575</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>92.56854428388894</v>
+        <v>4.431115853590128</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3563</v>
+        <v>3224</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>牧德</t>
+          <t>三顧</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>436.5492260787544</v>
+        <v>455.5613901365115</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>684</v>
+        <v>36.8</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.760325243691</v>
+        <v>55.37684587293788</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.16930020231564</v>
+        <v>24.63797840350205</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7688772697191297</v>
+        <v>1.064490791459104</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>9.288706380599486</v>
+        <v>0.2814236382594555</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>3312</v>
+        <v>3592</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>弘憶股</t>
+          <t>瑞鼎</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>430.9837508195923</v>
+        <v>445.3907212797503</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>50.5</v>
+        <v>244</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.15083507714177</v>
+        <v>49.11204283484098</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>29.3287902355381</v>
+        <v>33.13173123647515</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.641665912257937</v>
+        <v>0.8877225358544597</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.7752982131105068</v>
+        <v>2.574958113918338</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3324</v>
+        <v>3479</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>安勤</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>430.7718091080397</v>
+        <v>442.3533246452407</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1010</v>
+        <v>143</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>56.31889569398201</v>
+        <v>53.49090487187561</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.76125241932904</v>
+        <v>16.94432343552602</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.201883153428818</v>
+        <v>0.4023027898990143</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>20.17240906219741</v>
+        <v>-0.4909421766267287</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>3533</v>
+        <v>3661</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>426.9708447596621</v>
+        <v>441.9220853793421</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1960</v>
+        <v>3800</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.24494483202164</v>
+        <v>54.45548560347702</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>20.09876178765829</v>
+        <v>17.36339353751946</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8085942801108431</v>
+        <v>1.492208537934204</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>20.81188955270521</v>
+        <v>92.56854428388894</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3443</v>
+        <v>3563</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>牧德</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>425.3979513546499</v>
+        <v>436.5492260787544</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>4530</v>
+        <v>684</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.13806765017795</v>
+        <v>51.760325243691</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.62436112129201</v>
+        <v>20.16930020231564</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.041286456255137</v>
+        <v>0.7688772697191297</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>100.1514209440218</v>
+        <v>9.288706380599486</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>3665</v>
+        <v>3312</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>弘憶股</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>424.4478790950297</v>
+        <v>430.9837508195923</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2190</v>
+        <v>50.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.93480329351049</v>
+        <v>52.15083507714177</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11.25998577914002</v>
+        <v>29.3287902355381</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.093246326853806</v>
+        <v>1.641665912257937</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>18.27776396519518</v>
+        <v>0.7752982131105068</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3356</v>
+        <v>3324</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>奇偶</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>422.1589668544682</v>
+        <v>430.7718091080397</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>57.6</v>
+        <v>1010</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.50891209498354</v>
+        <v>56.31889569398201</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.96801186716192</v>
+        <v>23.76125241932904</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8199244817443984</v>
+        <v>1.201883153428818</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0460704558241333</v>
+        <v>20.17240906219741</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>3669</v>
+        <v>3533</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>圓展</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>421.4907110964894</v>
+        <v>426.9708447596621</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>38.6</v>
+        <v>1960</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.68172475300322</v>
+        <v>48.24494483202164</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.23860143171504</v>
+        <v>20.09876178765829</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.5074330948553059</v>
+        <v>0.8085942801108431</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0035977418517175</v>
+        <v>20.81188955270521</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>3130</v>
+        <v>3443</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>410.6447038530479</v>
+        <v>425.3979513546499</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>202.5</v>
+        <v>4530</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>26.10090394785182</v>
+        <v>56.13806765017795</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>47.21742428193819</v>
+        <v>14.62436112129201</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4904648117029492</v>
+        <v>1.041286456255137</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.397157554042697</v>
+        <v>100.1514209440218</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>3467</v>
+        <v>3665</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>台灣精材</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>404.1611701877189</v>
+        <v>424.4478790950297</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>45.05</v>
+        <v>2190</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>33.56308803297722</v>
+        <v>52.93480329351049</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>35.15278464228427</v>
+        <v>11.25998577914002</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7597486422515251</v>
+        <v>1.093246326853806</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1697060468081073</v>
+        <v>18.27776396519518</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>3289</v>
+        <v>3356</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>宜特</t>
+          <t>奇偶</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>399.2311922660289</v>
+        <v>422.1589668544682</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>140.5</v>
+        <v>57.6</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>42.65842313442428</v>
+        <v>49.50891209498354</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.45961683909779</v>
+        <v>16.96801186716192</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7200280071559568</v>
+        <v>0.8199244817443984</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.5462479819044628</v>
+        <v>0.0460704558241333</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>3701</v>
+        <v>3669</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>大眾控</t>
+          <t>圓展</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>399.0482353014956</v>
+        <v>421.4907110964894</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>41.15</v>
+        <v>38.6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.63544373125971</v>
+        <v>53.68172475300322</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>30.77755185995208</v>
+        <v>18.23860143171504</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8824662576145555</v>
+        <v>0.5074330948553059</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9514326099165172</v>
+        <v>0.0035977418517175</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>3303</v>
+        <v>3130</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>岱稜</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>395.4454186595691</v>
+        <v>410.6447038530479</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>56</v>
+        <v>202.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.20588978651445</v>
+        <v>26.10090394785182</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>14.51999528757445</v>
+        <v>47.21742428193819</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4058984575991612</v>
+        <v>0.4904648117029492</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3683618440742394</v>
+        <v>0.397157554042697</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>3306</v>
+        <v>3467</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>鼎天</t>
+          <t>台灣精材</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>394.9226684288632</v>
+        <v>404.1611701877189</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>44</v>
+        <v>45.05</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.10440768300855</v>
+        <v>33.56308803297722</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.87456805156631</v>
+        <v>35.15278464228427</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3748054426561498</v>
+        <v>0.7597486422515251</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0964099033247429</v>
+        <v>0.1697060468081073</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>3444</v>
+        <v>3289</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>利機</t>
+          <t>宜特</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>391.5715174879758</v>
+        <v>399.2311922660289</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>74</v>
+        <v>140.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.59723970998483</v>
+        <v>42.65842313442428</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>36.78496798927146</v>
+        <v>25.45961683909779</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.190593492563549</v>
+        <v>0.7200280071559568</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.198819957457867</v>
+        <v>0.5462479819044628</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>3227</v>
+        <v>3701</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>大眾控</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>384.533603637129</v>
+        <v>399.0482353014956</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>210</v>
+        <v>41.15</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>54.13289957120037</v>
+        <v>49.63544373125971</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17.20657573524086</v>
+        <v>30.77755185995208</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.079583724787318</v>
+        <v>0.8824662576145555</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>2.834806938028456</v>
+        <v>0.9514326099165172</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>3311</v>
+        <v>3303</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>岱稜</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>375.9734070715267</v>
+        <v>395.4454186595691</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>32.3</v>
+        <v>56</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>39.59322565995325</v>
+        <v>54.20588978651445</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>29.10236631911575</v>
+        <v>14.51999528757445</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7367172154056546</v>
+        <v>0.4058984575991612</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.019321665322781</v>
+        <v>0.3683618440742394</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>3484</v>
+        <v>3306</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>崧騰</t>
+          <t>鼎天</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>374.6152493184617</v>
+        <v>394.9226684288632</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>50.7</v>
+        <v>44</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.18238613204953</v>
+        <v>45.10440768300855</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.96625510868157</v>
+        <v>26.87456805156631</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.7975631087109349</v>
+        <v>0.3748054426561498</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.4401450133683928</v>
+        <v>0.0964099033247429</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>3150</v>
+        <v>3444</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>鈺寶-創</t>
+          <t>利機</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>374.1600143326716</v>
+        <v>391.5715174879758</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>17.75</v>
+        <v>74</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>56.61237865457052</v>
+        <v>47.59723970998483</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.15257226947684</v>
+        <v>36.78496798927146</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.809251896404884</v>
+        <v>2.190593492563549</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.187209796639902</v>
+        <v>1.198819957457867</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>3491</v>
+        <v>3527</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>聚積</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>370.6018234593568</v>
+        <v>388.2511654157353</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1235</v>
+        <v>52.1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.47576348756959</v>
+        <v>41.13716595656573</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.33399901474829</v>
+        <v>22.95683395386066</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8046168403064763</v>
+        <v>0.4695708136610143</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>36.90397755369293</v>
+        <v>0.0494623921649837</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>3485</v>
+        <v>3227</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>敘豐</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>370.4045419768052</v>
+        <v>384.533603637129</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>208.5</v>
+        <v>210</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>40.1407555604172</v>
+        <v>54.13289957120037</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>29.48001074866492</v>
+        <v>17.20657573524086</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6519298391819972</v>
+        <v>1.079583724787318</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>2.36661865265593</v>
+        <v>2.834806938028456</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>3357</v>
+        <v>3311</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>臺慶科</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>368.6743804105819</v>
+        <v>375.9734070715267</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>218</v>
+        <v>32.3</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.61813419311205</v>
+        <v>39.59322565995325</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>27.56678433554085</v>
+        <v>29.10236631911575</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8559042156921631</v>
+        <v>0.7367172154056546</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>3.631110299848665</v>
+        <v>-0.019321665322781</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>3349</v>
+        <v>3484</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>寶德</t>
+          <t>崧騰</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>367.6210945489682</v>
+        <v>374.6152493184617</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>23.25</v>
+        <v>50.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>56.52680178977196</v>
+        <v>54.18238613204953</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>33.33326830597907</v>
+        <v>21.96625510868157</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.15947874405403</v>
+        <v>0.7975631087109349</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1268697166212691</v>
+        <v>0.4401450133683928</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>3380</v>
+        <v>3150</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>明泰</t>
+          <t>鈺寶-創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>367.5221961937516</v>
+        <v>374.1600143326716</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>28.5</v>
+        <v>17.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.33908145869656</v>
+        <v>56.61237865457052</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>30.18720996070917</v>
+        <v>20.15257226947684</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6012286397867642</v>
+        <v>1.809251896404884</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0993315910916687</v>
+        <v>0.187209796639902</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>3712</v>
+        <v>3491</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>永崴投控</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>364.4794394276381</v>
+        <v>370.6018234593568</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>21.15</v>
+        <v>1235</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>67.65881529345322</v>
+        <v>50.47576348756959</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.67453504721818</v>
+        <v>14.33399901474829</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9344099275625288</v>
+        <v>0.8046168403064763</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.4058116173168701</v>
+        <v>36.90397755369293</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>3285</v>
+        <v>3485</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>微端</t>
+          <t>敘豐</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>362.3919534928519</v>
+        <v>370.4045419768052</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>38</v>
+        <v>208.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>47.38052842763002</v>
+        <v>40.1407555604172</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.86041077286521</v>
+        <v>29.48001074866492</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.200827285586965</v>
+        <v>0.6519298391819972</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1019960835204045</v>
+        <v>2.36661865265593</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>3481</v>
+        <v>3516</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>亞帝歐</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>361.0417518220564</v>
+        <v>369.4650685325666</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>52.3</v>
+        <v>26.2</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.7066163973079</v>
+        <v>52.24139555457776</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>30.13524839701561</v>
+        <v>18.34322885610096</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6449609769151559</v>
+        <v>0.2142077702686433</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.438160239644219</v>
+        <v>0.1383899849369238</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>3276</v>
+        <v>3357</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>宇環</t>
+          <t>臺慶科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>360.8988557937169</v>
+        <v>368.6743804105819</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>14.7</v>
+        <v>218</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.84513188733715</v>
+        <v>46.61813419311205</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.94396155366285</v>
+        <v>27.56678433554085</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2335651735416533</v>
+        <v>0.8559042156921631</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2195306631509613</v>
+        <v>3.631110299848665</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>3465</v>
+        <v>3526</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>進泰電子</t>
+          <t>凡甲</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>358.0909497708182</v>
+        <v>368.3259170326347</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>29.95</v>
+        <v>289</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>39.82741122112387</v>
+        <v>41.24733555887951</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19.5517333319506</v>
+        <v>24.05425917248072</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7727476094850638</v>
+        <v>0.9286711762664446</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0201766715411138</v>
+        <v>-0.2607115647835218</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>3455</v>
+        <v>3349</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>由田</t>
+          <t>寶德</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>357.3076971330317</v>
+        <v>367.6210945489682</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>205.5</v>
+        <v>23.25</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>53.41738148414733</v>
+        <v>56.52680178977196</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.38769858208726</v>
+        <v>33.33326830597907</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9686278656122116</v>
+        <v>1.15947874405403</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>1</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>4.124768148592096</v>
+        <v>-0.1268697166212691</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3232</v>
+        <v>3380</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>昱捷</t>
+          <t>明泰</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>353.1000275896592</v>
+        <v>367.5221961937516</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>19.6</v>
+        <v>28.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>33.16474675857725</v>
+        <v>42.33908145869656</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>50.14249694568561</v>
+        <v>30.18720996070917</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4558593207906267</v>
+        <v>0.6012286397867642</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0070194816194735</v>
+        <v>0.0993315910916687</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3596</v>
+        <v>3712</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>永崴投控</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>351.2363679708794</v>
+        <v>364.4794394276381</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>174</v>
+        <v>21.15</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.37382361354847</v>
+        <v>67.65881529345322</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26.47465056805721</v>
+        <v>15.67453504721818</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.428614089719143</v>
+        <v>0.9344099275625288</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1803434883035217</v>
+        <v>0.4058116173168701</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3528</v>
+        <v>3285</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>安馳</t>
+          <t>微端</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>349.8241788347872</v>
+        <v>362.3919534928519</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>38</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.2223144356849</v>
+        <v>47.38052842763002</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.57431844668216</v>
+        <v>15.86041077286521</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.9299755592797768</v>
+        <v>1.200827285586965</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.60350269978426</v>
+        <v>0.1019960835204045</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>3673</v>
+        <v>3481</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>349.5247236516737</v>
+        <v>361.0417518220564</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>63.3</v>
+        <v>52.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.15533781606701</v>
+        <v>51.7066163973079</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>30.30636306657896</v>
+        <v>30.13524839701561</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9276680446014191</v>
+        <v>0.6449609769151559</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.8971049088249572</v>
+        <v>0.438160239644219</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>3296</v>
+        <v>3276</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>勝德</t>
+          <t>宇環</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>341.520415321737</v>
+        <v>360.8988557937169</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>23.45</v>
+        <v>14.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>44.17906049625607</v>
+        <v>39.84513188733715</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.59895325618188</v>
+        <v>20.94396155366285</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2372830885931943</v>
+        <v>0.2335651735416533</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.14003304901483</v>
+        <v>-0.2195306631509613</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>3260</v>
+        <v>3465</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>進泰電子</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>340.1629510646929</v>
+        <v>358.0909497708182</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>411</v>
+        <v>29.95</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.08120254749856</v>
+        <v>39.82741122112387</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.87176613533874</v>
+        <v>19.5517333319506</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9167954809883518</v>
+        <v>0.7727476094850638</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>4.589258535686715</v>
+        <v>0.0201766715411138</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>3360</v>
+        <v>3455</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>尚立</t>
+          <t>由田</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>340.0581822905702</v>
+        <v>357.3076971330317</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>16.25</v>
+        <v>205.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.33451353477172</v>
+        <v>53.41738148414733</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.71937912455671</v>
+        <v>21.38769858208726</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.2600764492534325</v>
+        <v>0.9686278656122116</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>1</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1466117639604089</v>
+        <v>4.124768148592096</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>3221</v>
+        <v>3232</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>台嘉碩</t>
+          <t>昱捷</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>338.8425159829044</v>
+        <v>353.1000275896592</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>48.2</v>
+        <v>19.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.78784337900948</v>
+        <v>33.16474675857725</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.3472494920074</v>
+        <v>50.14249694568561</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5698239796948917</v>
+        <v>0.4558593207906267</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.4603861520875405</v>
+        <v>-0.0070194816194735</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>3209</v>
+        <v>3596</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>337.276440454224</v>
+        <v>351.2363679708794</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>55.8</v>
+        <v>174</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>43.97573587053896</v>
+        <v>42.37382361354847</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.42109687654261</v>
+        <v>26.47465056805721</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.680451939293875</v>
+        <v>2.428614089719143</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.396603545815092</v>
+        <v>-0.1803434883035217</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>3149</v>
+        <v>3528</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>正達</t>
+          <t>安馳</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>336.6943345647986</v>
+        <v>349.8241788347872</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>69</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.5011519944534</v>
+        <v>50.2223144356849</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>28.09393021840302</v>
+        <v>16.57431844668216</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.283023654775255</v>
+        <v>0.9299755592797768</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.140074804233464</v>
+        <v>1.60350269978426</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>3545</v>
+        <v>3673</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>敦泰</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>332.8154779882206</v>
+        <v>349.5247236516737</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>51.1</v>
+        <v>63.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.90033330954872</v>
+        <v>47.15533781606701</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.19894081726456</v>
+        <v>30.30636306657896</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7460149229098219</v>
+        <v>0.9276680446014191</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.557750705025033</v>
+        <v>0.8971049088249572</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>3288</v>
+        <v>3296</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>點晶</t>
+          <t>勝德</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>331.1806148229118</v>
+        <v>341.520415321737</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>22.55</v>
+        <v>23.45</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.31688414116252</v>
+        <v>44.17906049625607</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22.65517731557677</v>
+        <v>20.59895325618188</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4967342112939236</v>
+        <v>0.2372830885931943</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.4403821959902319</v>
+        <v>-0.14003304901483</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>3438</v>
+        <v>3260</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>類比科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>329.0037461952993</v>
+        <v>340.1629510646929</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>61.4</v>
+        <v>411</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>52.91876113426302</v>
+        <v>54.08120254749856</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>21.0649791995706</v>
+        <v>11.87176613533874</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5006989400632083</v>
+        <v>0.9167954809883518</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>1.29640135795761</v>
+        <v>4.589258535686715</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>3230</v>
+        <v>3360</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>錦明</t>
+          <t>尚立</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>328.1550994218188</v>
+        <v>340.0581822905702</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>40.8</v>
+        <v>16.25</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.99663363002192</v>
+        <v>43.33451353477172</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>18.42516735180787</v>
+        <v>22.71937912455671</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4101487096539588</v>
+        <v>0.2600764492534325</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>1</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.2361200203837365</v>
+        <v>-0.1466117639604089</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>3265</v>
+        <v>3523</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>326.8438050601691</v>
+        <v>338.9231472782421</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>164.5</v>
+        <v>15.75</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.46318433665773</v>
+        <v>49.42639319314134</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.70375920527601</v>
+        <v>14.3047503972562</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.919663282586042</v>
+        <v>0.2627529204953421</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>1</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.756850961641472</v>
+        <v>-0.0025773031319438</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>3715</v>
+        <v>3221</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>定穎投控</t>
+          <t>台嘉碩</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>317.7074983131524</v>
+        <v>338.8425159829044</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>125.5</v>
+        <v>48.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>49.6567075310119</v>
+        <v>47.78784337900948</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>36.71956328573527</v>
+        <v>18.3472494920074</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7992168371980003</v>
+        <v>0.5698239796948917</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>3.200587713220031</v>
+        <v>0.4603861520875405</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>3178</v>
+        <v>3209</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>公準</t>
+          <t>全科</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>309.2956722130068</v>
+        <v>337.276440454224</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>57.9</v>
+        <v>55.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.71100390419479</v>
+        <v>43.97573587053896</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.12782177092606</v>
+        <v>18.42109687654261</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.30328221072048</v>
+        <v>1.680451939293875</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1862400165739726</v>
+        <v>0.396603545815092</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3390</v>
+        <v>3149</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>旭軟</t>
+          <t>正達</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>307.7275990844557</v>
+        <v>336.6943345647986</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>22.85</v>
+        <v>69</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.11293874913609</v>
+        <v>44.5011519944534</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>31.63798600962006</v>
+        <v>28.09393021840302</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4610216458841753</v>
+        <v>1.283023654775255</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1218982598260991</v>
+        <v>-0.140074804233464</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3322</v>
+        <v>3545</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>建舜電</t>
+          <t>敦泰</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>305.4156181766162</v>
+        <v>332.8154779882206</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>11.4</v>
+        <v>51.1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.76703579380817</v>
+        <v>49.90033330954872</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>23.28638503998889</v>
+        <v>22.19894081726456</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3771551894834282</v>
+        <v>0.7460149229098219</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0327179352696129</v>
+        <v>0.557750705025033</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>3259</v>
+        <v>3288</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>鑫創</t>
+          <t>點晶</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>305.0935849914956</v>
+        <v>331.1806148229118</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>14.55</v>
+        <v>22.55</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>37.64141423134181</v>
+        <v>47.31688414116252</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>14.48403654875866</v>
+        <v>22.65517731557677</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.525470886068612</v>
+        <v>0.4967342112939236</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0005879100372826</v>
+        <v>-0.4403821959902319</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3373</v>
+        <v>3438</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>熱映</t>
+          <t>類比科</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>303.4284987085484</v>
+        <v>329.0037461952993</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>16.5</v>
+        <v>61.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.9602604165259</v>
+        <v>52.91876113426302</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.23492949642306</v>
+        <v>21.0649791995706</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3001538622778487</v>
+        <v>0.5006989400632083</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>1</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0100219881397743</v>
+        <v>1.29640135795761</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3593</v>
+        <v>3230</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>力銘</t>
+          <t>錦明</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>300.9877728079788</v>
+        <v>328.1550994218188</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>12.9</v>
+        <v>40.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>36.53838398863467</v>
+        <v>48.99663363002192</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>34.42749004661542</v>
+        <v>18.42516735180787</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.159166200491171</v>
+        <v>0.4101487096539588</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0475721540560899</v>
+        <v>-0.2361200203837365</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3588</v>
+        <v>3265</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>通嘉</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>298.9095203220178</v>
+        <v>326.8438050601691</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>57.9</v>
+        <v>164.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.76365433975035</v>
+        <v>52.46318433665773</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>24.61144377444301</v>
+        <v>18.70375920527601</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.378395340607328</v>
+        <v>1.919663282586042</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.7005769699498936</v>
+        <v>1.756850961641472</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>3219</v>
+        <v>3508</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>倚強股份</t>
+          <t>位速</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>298.2725429912622</v>
+        <v>326.4290541371212</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>16.85</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>56.60305584579922</v>
+        <v>48.97962713825383</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.58224376572796</v>
+        <v>15.37564188444677</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.162569018196978</v>
+        <v>0.6391611772468655</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1.531927209026624</v>
+        <v>0.2608436101170169</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>3217</v>
+        <v>3715</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>優群</t>
+          <t>定穎投控</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>297.9639762235975</v>
+        <v>317.7074983131524</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>149.5</v>
+        <v>125.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.04930722778583</v>
+        <v>49.6567075310119</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>35.56175528012919</v>
+        <v>36.71956328573527</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.999154379134052</v>
+        <v>0.7992168371980003</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.069829298999797</v>
+        <v>3.200587713220031</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>3268</v>
+        <v>3178</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>海德威</t>
+          <t>公準</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>297.8683268572222</v>
+        <v>309.2956722130068</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>20.45</v>
+        <v>57.9</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.40002761241392</v>
+        <v>41.71100390419479</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.43521948337759</v>
+        <v>15.12782177092606</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3471229839317237</v>
+        <v>0.30328221072048</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0319837881330037</v>
+        <v>-0.1862400165739726</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>3321</v>
+        <v>3390</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>同泰</t>
+          <t>旭軟</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>295.4843998961941</v>
+        <v>307.7275990844557</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>19.3</v>
+        <v>22.85</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>48.13733016907885</v>
+        <v>40.11293874913609</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.16417351993573</v>
+        <v>31.63798600962006</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6240068734831978</v>
+        <v>0.4610216458841753</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2188574688377866</v>
+        <v>0.1218982598260991</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>3290</v>
+        <v>3322</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>東浦</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>292.0093775755384</v>
+        <v>305.4156181766162</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>54.9</v>
+        <v>11.4</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.34432324996527</v>
+        <v>39.76703579380817</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>31.16420075605853</v>
+        <v>23.28638503998889</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7468607117346814</v>
+        <v>0.3771551894834282</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.3566796641168372</v>
+        <v>0.0327179352696129</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>3317</v>
+        <v>3259</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>尼克森</t>
+          <t>鑫創</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>287.3240750876866</v>
+        <v>305.0935849914956</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>14.55</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>41.55718339185626</v>
+        <v>37.64141423134181</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>26.45558184962182</v>
+        <v>14.48403654875866</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.287137029002401</v>
+        <v>1.525470886068612</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1900524991897416</v>
+        <v>0.0005879100372826</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>3501</v>
+        <v>3373</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>維熹</t>
+          <t>熱映</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>285.6339635566134</v>
+        <v>303.4284987085484</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>38.75</v>
+        <v>16.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.98367720045677</v>
+        <v>47.9602604165259</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10.51195367652217</v>
+        <v>15.23492949642306</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.1542113385253464</v>
+        <v>0.3001538622778487</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0936707694709053</v>
+        <v>-0.0100219881397743</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>3297</v>
+        <v>3593</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>杭特</t>
+          <t>力銘</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>281.8102888570223</v>
+        <v>300.9877728079788</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>28.2</v>
+        <v>12.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>48.66445844691386</v>
+        <v>36.53838398863467</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.06411577306981</v>
+        <v>34.42749004661542</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.2752882547304968</v>
+        <v>2.159166200491171</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0853281999245849</v>
+        <v>-0.0475721540560899</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>3413</v>
+        <v>3588</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>通嘉</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>275.6221227494861</v>
+        <v>298.9095203220178</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>307.5</v>
+        <v>57.9</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.61748697998493</v>
+        <v>52.76365433975035</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.83220916674209</v>
+        <v>24.61144377444301</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4014032755154878</v>
+        <v>1.378395340607328</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-1.855973649399278</v>
+        <v>0.7005769699498936</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>3191</v>
+        <v>3219</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>雲嘉南</t>
+          <t>倚強股份</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>275.3620289831666</v>
+        <v>298.2725429912622</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>18.55</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>51.44434425897344</v>
+        <v>56.60305584579922</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7.986428954240815</v>
+        <v>20.58224376572796</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.542891808026703</v>
+        <v>1.162569018196978</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1134037565373218</v>
+        <v>1.531927209026624</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>3169</v>
+        <v>3217</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>亞信</t>
+          <t>優群</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>274.3299109954117</v>
+        <v>297.9639762235975</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>103</v>
+        <v>149.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>50.62253225534945</v>
+        <v>46.04930722778583</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.66319337404112</v>
+        <v>35.56175528012919</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4085021735913449</v>
+        <v>1.999154379134052</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.7716638808580296</v>
+        <v>1.069829298999797</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>3607</v>
+        <v>3268</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>谷崧</t>
+          <t>海德威</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>269.4596767871306</v>
+        <v>297.8683268572222</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14.35</v>
+        <v>20.45</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.52140916703311</v>
+        <v>49.40002761241392</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>24.49258387172128</v>
+        <v>14.43521948337759</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.223148690784054</v>
+        <v>0.3471229839317237</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0549798521873192</v>
+        <v>0.0319837881330037</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3323</v>
+        <v>3321</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>加百裕</t>
+          <t>同泰</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>267.5471668586704</v>
+        <v>295.4843998961941</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>31.85</v>
+        <v>19.3</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>54.23686758314163</v>
+        <v>48.13733016907885</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>23.80450923232013</v>
+        <v>21.16417351993573</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.448455041764878</v>
+        <v>0.6240068734831978</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.4557223928046516</v>
+        <v>0.2188574688377866</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>3374</v>
+        <v>3290</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>精材</t>
+          <t>東浦</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>267.2207944383321</v>
+        <v>292.0093775755384</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>337</v>
+        <v>54.9</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>53.68020028234884</v>
+        <v>41.34432324996527</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>18.12970702827248</v>
+        <v>31.16420075605853</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3380253256718029</v>
+        <v>0.7468607117346814</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-3.862318788010883</v>
+        <v>-0.3566796641168372</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3419</v>
+        <v>3537</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>譁裕</t>
+          <t>堡達</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>263.0135322288904</v>
+        <v>290.1616918078569</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>12</v>
+        <v>51.9</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>39.0788843463532</v>
+        <v>39.30035934972946</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>28.28185196133314</v>
+        <v>34.03608891546987</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.9054693911405418</v>
+        <v>0.5326444442222493</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0446090679355532</v>
+        <v>0.5405786082246573</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3447</v>
+        <v>3317</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>展達</t>
+          <t>尼克森</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>261.0495569320238</v>
+        <v>287.3240750876866</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>27.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>33.89709865194897</v>
+        <v>41.55718339185626</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>40.0359292765546</v>
+        <v>26.45558184962182</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8864567838423746</v>
+        <v>0.287137029002401</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.2268057557498251</v>
+        <v>-0.1900524991897416</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>3332</v>
+        <v>3501</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>幸康</t>
+          <t>維熹</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>254.8284972746786</v>
+        <v>285.6339635566134</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>63.5</v>
+        <v>38.75</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.49234289677555</v>
+        <v>38.98367720045677</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>12.09007668397771</v>
+        <v>10.51195367652217</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.114682794802803</v>
+        <v>0.1542113385253464</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.4304851123240438</v>
+        <v>-0.0936707694709053</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>3535</v>
+        <v>3297</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>杭特</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>247.4533656018678</v>
+        <v>281.8102888570223</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>90.2</v>
+        <v>28.2</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>47.29123850528924</v>
+        <v>48.66445844691386</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>37.40485466835769</v>
+        <v>15.06411577306981</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7627060717240903</v>
+        <v>0.2752882547304968</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>1.978696255757169</v>
+        <v>0.0853281999245849</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>3372</v>
+        <v>3413</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>典範</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>242.2163002415006</v>
+        <v>275.6221227494861</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>16.4</v>
+        <v>307.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.50613515409181</v>
+        <v>44.61748697998493</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>29.60248183712816</v>
+        <v>11.83220916674209</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.9029562174058688</v>
+        <v>0.4014032755154878</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1646622280243985</v>
+        <v>-1.855973649399278</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>3168</v>
+        <v>3191</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>眾福科</t>
+          <t>雲嘉南</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>239.6010534999648</v>
+        <v>275.3620289831666</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>42.65</v>
+        <v>18.55</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>47.77794717731176</v>
+        <v>51.44434425897344</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.45255939296522</v>
+        <v>7.986428954240815</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8755937367969581</v>
+        <v>0.542891808026703</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1419675750537538</v>
+        <v>0.1134037565373218</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>3376</v>
+        <v>3169</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>亞信</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>238.1342289487756</v>
+        <v>274.3299109954117</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>183.5</v>
+        <v>103</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>47.06101170306926</v>
+        <v>50.62253225534945</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.6166837382893</v>
+        <v>13.66319337404112</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.566479998613896</v>
+        <v>0.4085021735913449</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>1.341811476031096</v>
+        <v>0.7716638808580296</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>3308</v>
+        <v>3607</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>聯德</t>
+          <t>谷崧</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>236.6741385715474</v>
+        <v>269.4596767871306</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>19.65</v>
+        <v>14.35</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.53952870134462</v>
+        <v>43.52140916703311</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.11127525272206</v>
+        <v>24.49258387172128</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6438106186784306</v>
+        <v>0.223148690784054</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0194760825506857</v>
+        <v>0.0549798521873192</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>3257</v>
+        <v>3323</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>虹冠電</t>
+          <t>加百裕</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>232.5231260953489</v>
+        <v>267.5471668586704</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>51.4</v>
+        <v>31.85</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>42.66125544163722</v>
+        <v>54.23686758314163</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>22.88617251589001</v>
+        <v>23.80450923232013</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3854827267696458</v>
+        <v>1.448455041764878</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.2389794574798411</v>
+        <v>0.4557223928046516</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>3313</v>
+        <v>3374</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>斐成</t>
+          <t>精材</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>230.6705012831581</v>
+        <v>267.2207944383321</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>10.4</v>
+        <v>337</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>35.761988902355</v>
+        <v>53.68020028234884</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>24.83263082034154</v>
+        <v>18.12970702827248</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.7602816267802504</v>
+        <v>0.3380253256718029</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.069405507558681</v>
+        <v>-3.862318788010883</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>3354</v>
+        <v>3419</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>律勝</t>
+          <t>譁裕</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>229.3527665391012</v>
+        <v>263.0135322288904</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>20.95</v>
+        <v>12</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>40.90870967302392</v>
+        <v>39.0788843463532</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>27.24131269783609</v>
+        <v>28.28185196133314</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5862546010891628</v>
+        <v>0.9054693911405418</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.2477217298106233</v>
+        <v>0.0446090679355532</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>3591</v>
+        <v>3447</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>艾笛森</t>
+          <t>展達</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>226.8745756726946</v>
+        <v>261.0495569320238</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>21.7</v>
+        <v>27.4</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>48.78924214139146</v>
+        <v>33.89709865194897</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>28.25399158248219</v>
+        <v>40.0359292765546</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4872489225199937</v>
+        <v>0.8864567838423746</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.2961759892023234</v>
+        <v>0.2268057557498251</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>3645</v>
+        <v>3332</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>達邁</t>
+          <t>幸康</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>226.3097512281806</v>
+        <v>254.8284972746786</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>47.00767361332302</v>
+        <v>51.49234289677555</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>35.11796582300276</v>
+        <v>12.09007668397771</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.801814729577468</v>
+        <v>1.114682794802803</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>1.386537020633932</v>
+        <v>-0.4304851123240438</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>3686</v>
+        <v>3492</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>達能</t>
+          <t>長盛</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>226.077635104227</v>
+        <v>250.1801841415948</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>14.9</v>
+        <v>21.95</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>42.49809050969321</v>
+        <v>44.67846935122238</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>19.42468385483691</v>
+        <v>9.06362981168258</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4833516257374125</v>
+        <v>4.065953897091591</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.041218217619249</v>
+        <v>0.0208381000886911</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>3530</v>
+        <v>3535</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>晶相光</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>225.677112958773</v>
+        <v>247.4533656018678</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>55.5</v>
+        <v>90.2</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>42.87277654132883</v>
+        <v>47.29123850528924</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>31.22692378994263</v>
+        <v>37.40485466835769</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.4994462563147231</v>
+        <v>0.7627060717240903</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.3255670201285259</v>
+        <v>1.978696255757169</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>3437</v>
+        <v>3372</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>榮創</t>
+          <t>典範</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>219.0393804550113</v>
+        <v>242.2163002415006</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>46.90264774563337</v>
+        <v>45.50613515409181</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>28.74732072993286</v>
+        <v>29.60248183712816</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.8783119559890481</v>
+        <v>0.9029562174058688</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.2584908571733149</v>
+        <v>0.1646622280243985</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>3152</v>
+        <v>3168</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>璟德</t>
+          <t>眾福科</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>212.3302737160421</v>
+        <v>239.6010534999648</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>220</v>
+        <v>42.65</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,16 +7336,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>45.93316335024829</v>
+        <v>47.77794717731176</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>15.55076312497693</v>
+        <v>11.45255939296522</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.9806421762117568</v>
+        <v>0.8755937367969581</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-1.924310769064862</v>
+        <v>0.1419675750537538</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>3163</v>
+        <v>3376</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>200.9155064412193</v>
+        <v>238.1342289487756</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>706</v>
+        <v>183.5</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,13 +7389,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>50.45615539775756</v>
+        <v>47.06101170306926</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>21.82165546539628</v>
+        <v>17.6166837382893</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.281232832858998</v>
+        <v>1.566479998613896</v>
       </c>
       <c r="K131" s="2" t="n">
         <v>0</v>
@@ -7407,31 +7407,31 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>17.55731753491035</v>
+        <v>1.341811476031096</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>3338</v>
+        <v>3308</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>泰碩</t>
+          <t>聯德</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>200.4377904473886</v>
+        <v>236.6741385715474</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>63.3</v>
+        <v>19.65</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7442,13 +7442,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>46.39437445168258</v>
+        <v>43.53952870134462</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>14.39888567055825</v>
+        <v>13.11127525272206</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.8180029803286673</v>
+        <v>0.6438106186784306</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>0.611169561613329</v>
+        <v>0.0194760825506857</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>3494</v>
+        <v>3511</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>誠研</t>
+          <t>矽瑪</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>196.5265087562805</v>
+        <v>234.23908588422</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>7.09</v>
+        <v>20.3</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>36.59167083792664</v>
+        <v>45.47803761737438</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>12.88070012569596</v>
+        <v>20.64020871355025</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.06392380560799</v>
+        <v>0.4755669889176832</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.003696954047056</v>
+        <v>0.1574570192868936</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>3694</v>
+        <v>3257</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>海華</t>
+          <t>虹冠電</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>179.322624088716</v>
+        <v>232.5231260953489</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>55.9</v>
+        <v>51.4</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>44.90723017745229</v>
+        <v>42.66125544163722</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>15.41577534416496</v>
+        <v>22.88617251589001</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.6772064751021819</v>
+        <v>0.3854827267696458</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0980145565970969</v>
+        <v>0.2389794574798411</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3483</v>
+        <v>3313</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>力致</t>
+          <t>斐成</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>178.9919174346961</v>
+        <v>230.6705012831581</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>74</v>
+        <v>10.4</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>38.72061743826353</v>
+        <v>35.761988902355</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>33.36752216266397</v>
+        <v>24.83263082034154</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.7122573228006363</v>
+        <v>0.7602816267802504</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.3536872299797782</v>
+        <v>-0.069405507558681</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7629,21 +7629,21 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>3128</v>
+        <v>3354</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>昇銳</t>
+          <t>律勝</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>163.9224854479534</v>
+        <v>229.3527665391012</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>21.95</v>
+        <v>20.95</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,16 +7654,16 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>46.39914790494319</v>
+        <v>40.90870967302392</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>24.52904645525333</v>
+        <v>27.24131269783609</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.4072946529527599</v>
+        <v>0.5862546010891628</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.1082841073081561</v>
+        <v>0.2477217298106233</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7682,21 +7682,21 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3294</v>
+        <v>3591</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>艾笛森</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>161.8786830996181</v>
+        <v>226.8745756726946</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>30.85</v>
+        <v>21.7</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,16 +7707,16 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>44.33206185744285</v>
+        <v>48.78924214139146</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>28.5564835916662</v>
+        <v>28.25399158248219</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.783275692528121</v>
+        <v>0.4872489225199937</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.3040125705389433</v>
+        <v>0.2961759892023234</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>3708</v>
+        <v>3645</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>上緯投控</t>
+          <t>達邁</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>150.3760129433028</v>
+        <v>226.3097512281806</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>102</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>52.78883545580144</v>
+        <v>47.00767361332302</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>17.7379058255259</v>
+        <v>35.11796582300276</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1.847580153779045</v>
+        <v>0.801814729577468</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>1.263951201639059</v>
+        <v>1.386537020633932</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3138</v>
+        <v>3686</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>達能</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>144.9133620128415</v>
+        <v>226.077635104227</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>99.8</v>
+        <v>14.9</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45.48591775330694</v>
+        <v>42.49809050969321</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>50.31172518628991</v>
+        <v>19.42468385483691</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.6807745331080834</v>
+        <v>0.4833516257374125</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>2.213796843834462</v>
+        <v>0.041218217619249</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>3272</v>
+        <v>3530</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>東碩</t>
+          <t>晶相光</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>123.2339432683998</v>
+        <v>225.677112958773</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>14.2</v>
+        <v>55.5</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>41.84464384832031</v>
+        <v>42.87277654132883</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>18.61761522558168</v>
+        <v>31.22692378994263</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.3734695556820605</v>
+        <v>0.4994462563147231</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.0567845970483934</v>
+        <v>0.3255670201285259</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>3207</v>
+        <v>3437</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>耀勝</t>
+          <t>榮創</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>112.3686464615735</v>
+        <v>219.0393804550113</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>42.4</v>
+        <v>18.1</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,16 +7919,16 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>30.44193165568618</v>
+        <v>46.90264774563337</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>44.89816906460417</v>
+        <v>28.74732072993286</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.5527462406489427</v>
+        <v>0.8783119559890481</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.3831299788268536</v>
+        <v>0.2584908571733149</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>3466</v>
+        <v>3152</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>德晉</t>
+          <t>璟德</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>104.2282431305842</v>
+        <v>212.3302737160421</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>25.85</v>
+        <v>220</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,16 +7972,16 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>35.84593224747921</v>
+        <v>45.93316335024829</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>28.41360157216132</v>
+        <v>15.55076312497693</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.9971770460514138</v>
+        <v>0.9806421762117568</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.1385267365723144</v>
+        <v>-1.924310769064862</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>3622</v>
+        <v>3512</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>皇龍</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>71.94893173138213</v>
+        <v>211.2925781777579</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>54.3</v>
+        <v>19.75</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,16 +8025,16 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>50.37505947659048</v>
+        <v>47.21343418389529</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>14.61863611869676</v>
+        <v>11.67233283327058</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.951942875891678</v>
+        <v>0.718231761326691</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.266849810343012</v>
+        <v>0.0569720884112629</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>3325</v>
+        <v>3163</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>旭品</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>67.43277619043138</v>
+        <v>200.9155064412193</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>11.9</v>
+        <v>706</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>42.26703261747168</v>
+        <v>50.45615539775756</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>11.62313098620698</v>
+        <v>21.82165546539628</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.5019770144005163</v>
+        <v>1.281232832858998</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,62 +8096,857 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.0067284353698322</v>
+        <v>17.55731753491035</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
+        <v>3338</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>泰碩</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>200.4377904473886</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>46.39437445168258</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>14.39888567055825</v>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>0.8180029803286673</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>0.611169561613329</v>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>3494</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>誠研</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>196.5265087562805</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>36.59167083792664</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>12.88070012569596</v>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>1.06392380560799</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N146" s="2" t="n">
+        <v>-0.003696954047056</v>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>3694</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>海華</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>179.322624088716</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>44.90723017745229</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>15.41577534416496</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.6772064751021819</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>-0.0980145565970969</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>3483</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>力致</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>178.9919174346961</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>38.72061743826353</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>33.36752216266397</v>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>0.7122573228006363</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" s="2" t="n">
+        <v>0.3536872299797782</v>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>3128</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>昇銳</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>163.9224854479534</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>46.39914790494319</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>24.52904645525333</v>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>0.4072946529527599</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" s="2" t="n">
+        <v>0.1082841073081561</v>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>3294</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>英濟</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>161.8786830996181</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>44.33206185744285</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>28.5564835916662</v>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>0.783275692528121</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N150" s="2" t="n">
+        <v>0.3040125705389433</v>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>3708</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>150.3760129433028</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>52.78883545580144</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>17.7379058255259</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>1.847580153779045</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N151" s="2" t="n">
+        <v>1.263951201639059</v>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>3521</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>鴻翊</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>148.3723829607216</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>47.3814270319628</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>15.85141834895845</v>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.2688461972577903</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" s="2" t="n">
+        <v>-0.0142090136356967</v>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>3138</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>耀登</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>144.9133620128415</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>45.48591775330694</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>50.31172518628991</v>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>0.6807745331080834</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>2.213796843834462</v>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>東碩</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>123.2339432683998</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>41.84464384832031</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>18.61761522558168</v>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>0.3734695556820605</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N154" s="2" t="n">
+        <v>0.0567845970483934</v>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>3207</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>耀勝</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>112.3686464615735</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>30.44193165568618</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>44.89816906460417</v>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0.5527462406489427</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N155" s="2" t="n">
+        <v>0.3831299788268536</v>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>3466</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>德晉</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>104.2282431305842</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>35.84593224747921</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>28.41360157216132</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>0.9971770460514138</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>-0.1385267365723144</v>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>3531</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>先益</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>75.88285580978825</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>51.95996846038116</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>7.982383112247825</v>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>0.8120790055851513</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N157" s="2" t="n">
+        <v>0.6337272803857432</v>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>3622</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>洋華</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>71.94893173138213</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>50.37505947659048</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>14.61863611869676</v>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>0.951942875891678</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N158" s="2" t="n">
+        <v>0.266849810343012</v>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>3325</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>旭品</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>67.43277619043138</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>42.26703261747168</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>11.62313098620698</v>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>0.5019770144005163</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N159" s="2" t="n">
+        <v>-0.0067284353698322</v>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
         <v>3206</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>志豐</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D145" s="2" t="n">
+      <c r="C160" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D160" s="2" t="n">
         <v>56.41157297965066</v>
       </c>
-      <c r="E145" s="2" t="n">
+      <c r="E160" s="2" t="n">
         <v>33.75</v>
       </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G145" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H145" s="2" t="n">
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H160" s="2" t="n">
         <v>43.462251652192</v>
       </c>
-      <c r="I145" s="2" t="n">
+      <c r="I160" s="2" t="n">
         <v>18.35034277935888</v>
       </c>
-      <c r="J145" s="2" t="n">
+      <c r="J160" s="2" t="n">
         <v>0.4235601846694837</v>
       </c>
-      <c r="K145" s="2" t="n">
+      <c r="K160" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N145" s="2" t="n">
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N160" s="2" t="n">
         <v>0.1596902867340861</v>
       </c>
-      <c r="O145" s="2" t="inlineStr">
+      <c r="O160" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
